--- a/artfynd/A 23207-2022 artfynd.xlsx
+++ b/artfynd/A 23207-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23207-2022 artfynd.xlsx
+++ b/artfynd/A 23207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1864122</v>
+        <v>257742</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543189.0905305239</v>
+        <v>543117</v>
       </c>
       <c r="R2" t="n">
-        <v>7044362.908462119</v>
+        <v>7044304</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-05-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1988179</v>
+        <v>408421</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543122.8985235663</v>
+        <v>543223</v>
       </c>
       <c r="R3" t="n">
-        <v>7044300.869599786</v>
+        <v>7044362</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2012-05-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>257742</v>
+        <v>1864122</v>
       </c>
       <c r="B4" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543117.4945138104</v>
+        <v>543189</v>
       </c>
       <c r="R4" t="n">
-        <v>7044303.920455165</v>
+        <v>7044363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2012-05-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2068718</v>
+        <v>1988179</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543114.7887427561</v>
+        <v>543123</v>
       </c>
       <c r="R5" t="n">
-        <v>7044371.719563805</v>
+        <v>7044301</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2012-05-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,6 +1072,107 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2068718</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nyflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543115</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7044372</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-05-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-05-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Stenman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 23207-2022 artfynd.xlsx
+++ b/artfynd/A 23207-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/257742</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/408421</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1864122</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1988179</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2068718</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>